--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -21060,16 +21060,16 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O127" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.04774655365375727</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21604,16 +21604,16 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O130" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.1550375939033637</v>
+        <v>0.1627894735985319</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -24568,16 +24568,16 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3148</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -23092,16 +23092,16 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O136" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1627894735985319</v>
+        <v>0.1647274435223239</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -26056,16 +26056,16 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O154" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26678,6 +26678,154 @@
       <c r="BC157" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>2</v>
+      </c>
+      <c r="O158" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26714,7 +26862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26945,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -26807,7 +26955,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -26859,7 +27007,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3162</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>35</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.3885522299678568</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1753,9 +1744,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -1901,9 +1889,6 @@
       <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -2546,7 +2531,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2693,9 +2678,6 @@
       <c r="O13" t="n">
         <v>14</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.1308283259959668</v>
       </c>
@@ -4717,9 +4699,6 @@
       <c r="O26" t="n">
         <v>23</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2553343225503059</v>
       </c>
@@ -5013,9 +4992,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -5409,9 +5385,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5557,9 +5530,6 @@
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -5705,9 +5675,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -6350,7 +6317,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6497,9 +6464,6 @@
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1121385651394002</v>
       </c>
@@ -8225,9 +8189,6 @@
       <c r="O47" t="n">
         <v>21</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.2331313379807141</v>
       </c>
@@ -8521,9 +8482,6 @@
       <c r="O49" t="n">
         <v>4</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.07115236683456549</v>
       </c>
@@ -8917,9 +8875,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -9065,9 +9020,6 @@
       <c r="O52" t="n">
         <v>6</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.01162781954275227</v>
       </c>
@@ -9213,9 +9165,6 @@
       <c r="O53" t="n">
         <v>4</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.07075903303182025</v>
       </c>
@@ -9858,7 +9807,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -10005,9 +9954,6 @@
       <c r="O57" t="n">
         <v>13</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -11585,9 +11531,6 @@
       <c r="O67" t="n">
         <v>17</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.06243780093183643</v>
       </c>
@@ -11733,9 +11676,6 @@
       <c r="O68" t="n">
         <v>17</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.1887253688415304</v>
       </c>
@@ -12029,9 +11969,6 @@
       <c r="O70" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -12425,9 +12362,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12573,9 +12507,6 @@
       <c r="O73" t="n">
         <v>17</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.03294548870446478</v>
       </c>
@@ -12721,9 +12652,6 @@
       <c r="O74" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -13117,9 +13045,6 @@
       <c r="O76" t="n">
         <v>6</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.1134756279883097</v>
       </c>
@@ -13366,7 +13291,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -13513,9 +13438,6 @@
       <c r="O78" t="n">
         <v>13</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -15093,9 +15015,6 @@
       <c r="O88" t="n">
         <v>24</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.08814748366847497</v>
       </c>
@@ -15241,9 +15160,6 @@
       <c r="O89" t="n">
         <v>18</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -15537,9 +15453,6 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -15933,9 +15846,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -16081,9 +15991,6 @@
       <c r="O94" t="n">
         <v>51</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.09883646611339433</v>
       </c>
@@ -16229,9 +16136,6 @@
       <c r="O95" t="n">
         <v>5</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -16625,9 +16529,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16874,7 +16775,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -17021,9 +16922,6 @@
       <c r="O99" t="n">
         <v>8</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.07475904342626677</v>
       </c>
@@ -18749,9 +18647,6 @@
       <c r="O110" t="n">
         <v>4</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -18897,9 +18792,6 @@
       <c r="O111" t="n">
         <v>33</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.1212027900441531</v>
       </c>
@@ -19045,9 +18937,6 @@
       <c r="O112" t="n">
         <v>18</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.1998268611263263</v>
       </c>
@@ -19341,9 +19230,6 @@
       <c r="O114" t="n">
         <v>3</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -19737,9 +19623,6 @@
       <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -19885,9 +19768,6 @@
       <c r="O117" t="n">
         <v>80</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.1550375939033637</v>
       </c>
@@ -20033,9 +19913,6 @@
       <c r="O118" t="n">
         <v>5</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.08844879128977531</v>
       </c>
@@ -20429,9 +20306,6 @@
       <c r="O120" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -20678,7 +20552,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -20825,9 +20699,6 @@
       <c r="O122" t="n">
         <v>13</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.1214834455676835</v>
       </c>
@@ -21221,9 +21092,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -21369,9 +21237,6 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -21517,9 +21382,6 @@
       <c r="O126" t="n">
         <v>11</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -21665,9 +21527,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -21813,9 +21672,6 @@
       <c r="O128" t="n">
         <v>7</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -21961,9 +21817,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22109,9 +21962,6 @@
       <c r="O130" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.002578534319492447</v>
       </c>
@@ -22257,9 +22107,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -22405,9 +22252,6 @@
       <c r="O132" t="n">
         <v>11</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -22553,9 +22397,6 @@
       <c r="O133" t="n">
         <v>13</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.04774655365375727</v>
       </c>
@@ -22701,9 +22542,6 @@
       <c r="O134" t="n">
         <v>4</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.07115236683456549</v>
       </c>
@@ -23097,9 +22935,6 @@
       <c r="O136" t="n">
         <v>85</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.1647274435223239</v>
       </c>
@@ -23245,9 +23080,6 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -23641,9 +23473,6 @@
       <c r="O139" t="n">
         <v>12</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.1121385651394002</v>
       </c>
@@ -24037,9 +23866,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -24185,9 +24011,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -24333,9 +24156,6 @@
       <c r="O143" t="n">
         <v>14</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.00401105338587714</v>
       </c>
@@ -24481,9 +24301,6 @@
       <c r="O144" t="n">
         <v>4</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.003267233630263065</v>
       </c>
@@ -24629,9 +24446,6 @@
       <c r="O145" t="n">
         <v>6</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -24777,9 +24591,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -24925,9 +24736,6 @@
       <c r="O147" t="n">
         <v>13</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -25073,9 +24881,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -25221,9 +25026,6 @@
       <c r="O149" t="n">
         <v>10</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -25369,9 +25171,6 @@
       <c r="O150" t="n">
         <v>3</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.002450425222697299</v>
       </c>
@@ -25517,9 +25316,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -25665,9 +25461,6 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -26056,16 +25849,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O154" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R154" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26209,9 +25999,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -26605,9 +26392,6 @@
       <c r="O157" t="n">
         <v>15</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.004297557199154077</v>
       </c>
@@ -26753,9 +26537,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -26826,6 +26607,151 @@
       <c r="BC158" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>19</v>
+      </c>
+      <c r="O159" t="n">
+        <v>19</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26862,7 +26788,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26871,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -26955,7 +26881,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -27007,7 +26933,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3167</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -22930,13 +22930,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O136" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1647274435223239</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -25849,13 +25849,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O154" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R154" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26752,6 +26752,151 @@
       <c r="BC159" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26788,7 +26933,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -26871,7 +27016,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -26881,7 +27026,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -26933,7 +27078,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3188</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -22498,12 +22498,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22537,95 +22537,84 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>4</v>
+        <v>523</v>
       </c>
       <c r="O134" t="n">
-        <v>4</v>
+        <v>523</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.03701569715078964</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -22652,7 +22641,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -22701,98 +22690,23 @@
       <c r="O135" t="n">
         <v>4</v>
       </c>
+      <c r="R135" t="n">
+        <v>0.07115236683456549</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -22886,17 +22800,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22930,81 +22844,170 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="O136" t="n">
-        <v>83</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.1608515036747398</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
+        <v>1</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23036,12 +23039,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23075,95 +23078,81 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="R137" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23190,7 +23179,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -23239,98 +23228,23 @@
       <c r="O138" t="n">
         <v>3</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -23424,17 +23338,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23468,22 +23382,39 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
-        <v>12</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.1121385651394002</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -23491,6 +23422,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23508,7 +23497,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -23521,42 +23510,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23583,7 +23572,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -23632,98 +23621,23 @@
       <c r="O140" t="n">
         <v>12</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.1121385651394002</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MALARIA</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -23817,17 +23731,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23861,81 +23775,170 @@
         </is>
       </c>
       <c r="N141" t="n">
+        <v>12</v>
+      </c>
+      <c r="O141" t="n">
+        <v>12</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
         <v>1</v>
       </c>
-      <c r="R141" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
-      <c r="AT141" t="n">
-        <v>0</v>
-      </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -23967,12 +23970,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23997,7 +24000,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24006,13 +24009,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24045,42 +24048,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24112,12 +24115,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24151,13 +24154,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.00401105338587714</v>
+        <v>0</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24190,42 +24193,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24257,12 +24260,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24287,7 +24290,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24296,13 +24299,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O144" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R144" t="n">
-        <v>0.003267233630263065</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24335,42 +24338,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24402,12 +24405,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24441,13 +24444,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R145" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24480,42 +24483,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24547,12 +24550,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24577,7 +24580,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -24586,13 +24589,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24625,42 +24628,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24692,12 +24695,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24731,13 +24734,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.003724549572600201</v>
+        <v>0</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24770,42 +24773,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24837,12 +24840,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -24867,7 +24870,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24876,13 +24879,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R148" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -24915,42 +24918,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24982,12 +24985,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25021,13 +25024,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25060,42 +25063,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25127,12 +25130,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25157,7 +25160,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25166,13 +25169,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R150" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25205,42 +25208,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25272,12 +25275,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25302,22 +25305,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25350,42 +25353,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25417,12 +25420,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25456,95 +25459,81 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25571,7 +25560,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -25620,98 +25609,23 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
+      <c r="R153" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -25805,17 +25719,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -25849,81 +25763,170 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>23</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.04457330824721705</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25955,12 +25958,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25994,95 +25997,81 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="R155" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26109,7 +26098,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -26158,98 +26147,23 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
+      <c r="R156" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -26343,17 +26257,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26387,81 +26301,170 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>15</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.004297557199154077</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26493,12 +26496,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26523,7 +26526,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -26532,13 +26535,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O158" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R158" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26571,42 +26574,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26638,12 +26641,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26668,7 +26671,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -26677,13 +26680,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="R159" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -26716,42 +26719,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26783,12 +26786,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26813,7 +26816,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -26822,13 +26825,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -26861,40 +26864,185 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW160" t="inlineStr">
+      <c r="AW161" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX160" t="inlineStr">
+      <c r="AX161" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr">
+      <c r="AY161" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ160" t="inlineStr">
+      <c r="AZ161" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA160" t="inlineStr">
+      <c r="BA161" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB160" t="inlineStr">
+      <c r="BB161" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC160" t="inlineStr">
+      <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27016,7 +27164,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10">
@@ -27026,7 +27174,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -27078,7 +27226,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3191</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="16">
@@ -27088,7 +27236,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -25604,13 +25604,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25763,10 +25763,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O154" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -27045,6 +27045,151 @@
       <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>8</v>
+      </c>
+      <c r="O162" t="n">
+        <v>8</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.002292030506215508</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27226,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -27164,7 +27309,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -27174,7 +27319,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -27226,7 +27371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3714</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -25604,13 +25604,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R153" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25763,10 +25763,10 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3723</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -23577,12 +23577,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23616,13 +23616,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.1121385651394002</v>
+        <v>0</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -23656,7 +23656,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -23669,42 +23669,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23736,12 +23736,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23775,24 +23775,24 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -23857,17 +23857,17 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly malaria notifications.</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -23903,42 +23903,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23970,12 +23970,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24009,81 +24009,95 @@
         </is>
       </c>
       <c r="N142" t="n">
+        <v>12</v>
+      </c>
+      <c r="O142" t="n">
+        <v>12</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.1121385651394002</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
         <v>1</v>
       </c>
-      <c r="O142" t="n">
-        <v>1</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
-      <c r="AT142" t="n">
-        <v>0</v>
-      </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24110,17 +24124,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24145,7 +24159,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24154,81 +24168,170 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24260,12 +24363,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24290,7 +24393,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24299,13 +24402,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24338,42 +24441,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24538,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24444,13 +24547,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0.003267233630263065</v>
+        <v>0</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24580,7 +24683,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -24589,13 +24692,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O146" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R146" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.00401105338587714</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -24725,7 +24828,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24734,13 +24837,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -24870,7 +24973,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24879,13 +24982,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O148" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="R148" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25015,7 +25118,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25024,13 +25127,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25160,7 +25263,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25169,13 +25272,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O150" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R150" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25305,7 +25408,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25314,13 +25417,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25420,12 +25523,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25450,22 +25553,22 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25498,42 +25601,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25565,12 +25668,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -25595,104 +25698,90 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25719,17 +25808,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -25763,170 +25852,81 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
-        <v>4</v>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AT154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV154" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25958,12 +25958,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -25997,81 +25997,95 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O155" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="R155" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26098,17 +26112,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26142,29 +26156,104 @@
         </is>
       </c>
       <c r="N156" t="n">
+        <v>5</v>
+      </c>
+      <c r="O156" t="n">
+        <v>5</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
         <v>1</v>
       </c>
-      <c r="O156" t="n">
-        <v>1</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26177,12 +26266,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
+          <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -26190,47 +26279,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26257,17 +26346,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26301,170 +26390,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.0717048871803057</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26496,12 +26496,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26535,81 +26535,95 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O158" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R158" t="n">
-        <v>0.004297557199154077</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26636,17 +26650,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26671,7 +26685,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -26680,81 +26694,170 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O159" t="n">
-        <v>2</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26816,7 +26919,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -26825,13 +26928,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O160" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R160" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -26961,7 +27064,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -26970,13 +27073,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27106,7 +27209,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27115,13 +27218,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="O162" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="R162" t="n">
-        <v>0.002292030506215508</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27190,6 +27293,441 @@
       <c r="BC162" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>8</v>
+      </c>
+      <c r="O164" t="n">
+        <v>8</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.002292030506215508</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27226,7 +27764,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -27309,7 +27847,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -27319,7 +27857,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -27339,7 +27877,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -27371,7 +27909,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3724</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -25852,13 +25852,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26390,13 +26390,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O157" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R157" t="n">
-        <v>0.0717048871803057</v>
+        <v>0.07364285710409775</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3743</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -33283,12 +33283,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -33322,13 +33322,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="O189" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="R189" t="n">
-        <v>0.1608515036747398</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -33361,42 +33361,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33428,12 +33428,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -33467,95 +33467,81 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="O190" t="n">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="R190" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33582,7 +33568,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -33631,98 +33617,23 @@
       <c r="O191" t="n">
         <v>3</v>
       </c>
+      <c r="R191" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN191" t="b">
-        <v>1</v>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
@@ -33816,17 +33727,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -33860,22 +33771,39 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
-      </c>
-      <c r="R192" t="n">
-        <v>0</v>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -33883,6 +33811,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN192" t="b">
+        <v>1</v>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33900,7 +33886,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
+          <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -33913,42 +33899,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33975,7 +33961,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -34024,98 +34010,23 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U193" t="inlineStr">
         <is>
           <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>SER_NZ_MALARIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly malaria notifications.</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN193" t="b">
-        <v>1</v>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
@@ -34209,17 +34120,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -34253,22 +34164,39 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>12</v>
-      </c>
-      <c r="R194" t="n">
-        <v>0.1121385651394002</v>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -34276,6 +34204,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly malaria notifications.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34293,7 +34279,7 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+          <t>SER_NZ_MALARIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT194" t="n">
@@ -34306,42 +34292,42 @@
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34368,7 +34354,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -34417,98 +34403,23 @@
       <c r="O195" t="n">
         <v>12</v>
       </c>
+      <c r="R195" t="n">
+        <v>0.1121385651394002</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MALARIA</t>
         </is>
       </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MALARIA</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM195" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN195" t="b">
-        <v>1</v>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
@@ -34602,17 +34513,17 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -34646,81 +34557,170 @@
         </is>
       </c>
       <c r="N196" t="n">
+        <v>12</v>
+      </c>
+      <c r="O196" t="n">
+        <v>12</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
         <v>1</v>
       </c>
-      <c r="O196" t="n">
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
         <v>1</v>
       </c>
-      <c r="R196" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
-      <c r="AT196" t="n">
-        <v>0</v>
-      </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34752,12 +34752,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -34791,13 +34791,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -34830,42 +34830,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34897,12 +34897,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -34936,13 +34936,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.00401105338587714</v>
+        <v>0</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -34975,42 +34975,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35042,12 +35042,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35072,7 +35072,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -35081,93 +35081,81 @@
         </is>
       </c>
       <c r="N199" t="n">
+        <v>14</v>
+      </c>
+      <c r="O199" t="n">
+        <v>14</v>
+      </c>
+      <c r="R199" t="n">
+        <v>0.00401105338587714</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="n">
         <v>0</v>
       </c>
-      <c r="O199" t="n">
-        <v>0</v>
-      </c>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="R199" t="n">
-        <v>0</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT199" t="n">
-        <v>2</v>
-      </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35194,7 +35182,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -35246,98 +35234,18 @@
       <c r="P200" t="n">
         <v>0</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R200" t="n">
+        <v>0</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>1</v>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
@@ -35431,17 +35339,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -35466,7 +35374,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -35475,81 +35383,173 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>4</v>
-      </c>
-      <c r="R201" t="n">
-        <v>0.003267233630263065</v>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>0</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN201" t="b">
+        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -35581,12 +35581,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -35620,13 +35620,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O202" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R202" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.003267233630263065</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -35659,42 +35659,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35726,12 +35726,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -35756,7 +35756,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -35765,93 +35765,81 @@
         </is>
       </c>
       <c r="N203" t="n">
+        <v>6</v>
+      </c>
+      <c r="O203" t="n">
+        <v>6</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="n">
         <v>0</v>
       </c>
-      <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
-      <c r="AT203" t="n">
-        <v>2</v>
-      </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35878,7 +35866,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -35930,98 +35918,18 @@
       <c r="P204" t="n">
         <v>0</v>
       </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R204" t="n">
+        <v>0</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -36115,17 +36023,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -36150,7 +36058,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -36164,76 +36072,168 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="R205" t="n">
+      <c r="P205" t="n">
         <v>0</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN205" t="b">
+        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36265,12 +36265,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36304,13 +36304,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>0.003724549572600201</v>
+        <v>0</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -36343,42 +36343,42 @@
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36410,12 +36410,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -36440,7 +36440,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -36449,93 +36449,81 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O207" t="n">
-        <v>1</v>
-      </c>
-      <c r="P207" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R207" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA207" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS207" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36562,7 +36550,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -36614,98 +36602,18 @@
       <c r="P208" t="n">
         <v>1</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W208" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X208" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y208" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R208" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD208" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE208" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG208" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ208" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM208" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN208" t="b">
-        <v>1</v>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
@@ -36799,17 +36707,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -36834,7 +36742,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -36848,76 +36756,168 @@
       <c r="O209" t="n">
         <v>1</v>
       </c>
-      <c r="R209" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P209" t="n">
+        <v>1</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN209" t="b">
+        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36949,12 +36949,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -36988,13 +36988,13 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O210" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>0.002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
@@ -37027,42 +37027,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37094,12 +37094,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37124,7 +37124,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -37133,13 +37133,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O211" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R211" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.002865038132769385</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -37172,42 +37172,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37239,12 +37239,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37278,93 +37278,81 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O212" t="n">
-        <v>2</v>
-      </c>
-      <c r="P212" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R212" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37391,7 +37379,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -37443,98 +37431,18 @@
       <c r="P213" t="n">
         <v>2</v>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R213" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
       </c>
       <c r="AO213" t="inlineStr">
         <is>
@@ -37628,17 +37536,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -37663,90 +37571,182 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N214" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O214" t="n">
-        <v>5</v>
-      </c>
-      <c r="R214" t="n">
-        <v>0.01836405909759895</v>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P214" t="n">
+        <v>2</v>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD214" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN214" t="b">
+        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37778,12 +37778,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -37817,95 +37817,81 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O215" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R215" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.02203687091711874</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37932,7 +37918,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -37981,98 +37967,23 @@
       <c r="O216" t="n">
         <v>5</v>
       </c>
+      <c r="R216" t="n">
+        <v>0.08894045854320688</v>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U216" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_190</t>
         </is>
       </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_190</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN216" t="b">
-        <v>1</v>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
@@ -38166,17 +38077,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -38210,81 +38121,170 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="O217" t="n">
-        <v>38</v>
-      </c>
-      <c r="R217" t="n">
-        <v>0.07364285710409775</v>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD217" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 190.</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN217" t="b">
+        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_190</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38316,12 +38316,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38355,95 +38355,81 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="O218" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="R218" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.07558082702788979</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38470,7 +38456,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -38519,98 +38505,23 @@
       <c r="O219" t="n">
         <v>4</v>
       </c>
+      <c r="R219" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>SER_NO_FHI_501_MONTHLY</t>
         </is>
       </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_501_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN219" t="b">
-        <v>1</v>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
@@ -38704,17 +38615,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -38748,81 +38659,170 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O220" t="n">
-        <v>15</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0.004297557199154077</v>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD220" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF220" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG220" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH220" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM220" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN220" t="b">
+        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_501_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38854,12 +38854,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -38884,7 +38884,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -38893,13 +38893,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="R221" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.004297557199154077</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -38932,42 +38932,42 @@
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38999,12 +38999,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39038,93 +39038,81 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O222" t="n">
-        <v>1</v>
-      </c>
-      <c r="P222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R222" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39151,7 +39139,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -39203,98 +39191,18 @@
       <c r="P223" t="n">
         <v>1</v>
       </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R223" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN223" t="b">
-        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
@@ -39388,17 +39296,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -39423,7 +39331,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -39432,81 +39340,173 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O224" t="n">
-        <v>19</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0.005443572452261832</v>
-      </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN224" t="b">
+        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -39538,12 +39538,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -39568,7 +39568,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -39577,13 +39577,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R225" t="n">
-        <v>0</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -39616,42 +39616,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39683,12 +39683,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -39727,9 +39727,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="P226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -39738,77 +39735,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39835,7 +39823,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -39887,98 +39875,18 @@
       <c r="P227" t="n">
         <v>0</v>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R227" t="n">
+        <v>0</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -40072,17 +39980,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40107,7 +40015,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -40116,81 +40024,173 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>8</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0.002292030506215508</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>0</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40222,12 +40222,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40252,7 +40252,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -40261,13 +40261,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R229" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -40300,42 +40300,42 @@
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40367,12 +40367,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40406,93 +40406,81 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O230" t="n">
-        <v>2</v>
-      </c>
-      <c r="P230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA230" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ230" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40519,7 +40507,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -40571,98 +40559,18 @@
       <c r="P231" t="n">
         <v>2</v>
       </c>
-      <c r="U231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="V231" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MALARIA</t>
-        </is>
-      </c>
-      <c r="W231" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X231" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="Y231" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R231" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC231" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD231" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE231" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG231" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ231" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK231" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM231" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN231" t="b">
-        <v>1</v>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
@@ -40756,123 +40664,360 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>2</v>
+      </c>
+      <c r="O232" t="n">
+        <v>2</v>
+      </c>
+      <c r="P232" t="n">
+        <v>2</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD232" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF232" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG232" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ232" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM232" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN232" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MALARIA; SER_SG_HIST_MALARIA</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>malaria</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>D037</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>Malaria</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
         <is>
           <t>疟疾</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="K233" t="inlineStr">
         <is>
           <t>Parasitic</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N232" t="n">
+      <c r="N233" t="n">
         <v>14</v>
       </c>
-      <c r="O232" t="n">
+      <c r="O233" t="n">
         <v>14</v>
       </c>
-      <c r="R232" t="n">
+      <c r="R233" t="n">
         <v>0.00401105338587714</v>
       </c>
-      <c r="S232" t="inlineStr">
+      <c r="S233" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO232" t="inlineStr">
+      <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP232" t="inlineStr">
+      <c r="AP233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR232" t="inlineStr">
+      <c r="AR233" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS232" t="inlineStr"/>
-      <c r="AT232" t="n">
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="n">
         <v>0</v>
       </c>
-      <c r="AU232" t="inlineStr">
+      <c r="AU233" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV232" t="inlineStr">
+      <c r="AV233" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW232" t="inlineStr">
+      <c r="AW233" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX232" t="inlineStr">
+      <c r="AX233" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY232" t="inlineStr">
+      <c r="AY233" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ232" t="inlineStr">
+      <c r="AZ233" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA232" t="inlineStr">
+      <c r="BA233" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB232" t="inlineStr">
+      <c r="BB233" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC232" t="inlineStr">
+      <c r="BC233" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -40994,7 +41139,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -41004,7 +41149,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -41056,7 +41201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3787</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d037/2026-2029.xlsx
+++ b/diseases/d037/2026-2029.xlsx
@@ -53019,13 +53019,13 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O291" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R291" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.08447467184895517</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -63565,13 +63565,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O352" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R352" t="n">
-        <v>0.08333270672305797</v>
+        <v>0.08139473679926593</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -67542,13 +67542,13 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R375" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
@@ -68201,7 +68201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4916</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="16">
